--- a/docs/_baseline/bird_bulk.xlsx
+++ b/docs/_baseline/bird_bulk.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160">
   <si>
     <t>※ 엑셀 기반 수질/생태계 데이터 베이스 작성/관리 시 주의 사항</t>
   </si>
@@ -132,6 +132,12 @@
     <t>황조롱이</t>
   </si>
   <si>
+    <t>까치</t>
+  </si>
+  <si>
+    <t>물총새</t>
+  </si>
+  <si>
     <t>학명(필수X)</t>
   </si>
   <si>
@@ -148,6 +154,12 @@
   </si>
   <si>
     <t>Falco tinnunculus</t>
+  </si>
+  <si>
+    <t>Pica serica</t>
+  </si>
+  <si>
+    <t>Alcedo atthis</t>
   </si>
   <si>
     <t>특징</t>
@@ -207,7 +219,10 @@
 WV:겨울철새 / PM:통과철새</t>
   </si>
   <si>
-    <t>텃새</t>
+    <t>RES</t>
+  </si>
+  <si>
+    <t>SV</t>
   </si>
   <si>
     <t>서식지 유형</t>
@@ -260,6 +275,12 @@
   </si>
   <si>
     <t>비행</t>
+  </si>
+  <si>
+    <t>교목</t>
+  </si>
+  <si>
+    <t>횃대</t>
   </si>
   <si>
     <t>서식 유형, 아래 항목 중 택</t>
@@ -1594,7 +1615,7 @@
       <c r="H1" s="38"/>
       <c r="I1" s="44"/>
       <c r="J1" s="9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="K1" s="38"/>
       <c r="L1" s="38"/>
@@ -1605,21 +1626,21 @@
       <c r="Q1" s="38"/>
       <c r="R1" s="56"/>
       <c r="S1" s="60" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="T1" s="60" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U1" s="63" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="V1" s="63"/>
       <c r="W1" s="71"/>
       <c r="X1" s="71" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="Y1" s="80" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" ht="21" s="87" customFormat="true" customHeight="true">
@@ -1645,48 +1666,48 @@
         <v>32</v>
       </c>
       <c r="H2" s="39" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I2" s="45" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K2" s="40"/>
       <c r="L2" s="40"/>
       <c r="M2" s="22" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="N2" s="40"/>
       <c r="O2" s="40"/>
       <c r="P2" s="22" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="Q2" s="54" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="R2" s="57"/>
       <c r="S2" s="61" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="T2" s="61" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="U2" s="64" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="V2" s="69" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="W2" s="72" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="X2" s="78" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="Y2" s="81" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" ht="148.5" s="87" customFormat="true" customHeight="true">
@@ -1709,47 +1730,47 @@
       <c r="G3" s="33"/>
       <c r="H3" s="40"/>
       <c r="I3" s="45" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J3" s="50" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="L3" s="22" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="M3" s="22" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N3" s="22" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O3" s="22" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P3" s="22" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="Q3" s="55"/>
       <c r="R3" s="58" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="S3" s="61" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="T3" s="61" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="U3" s="65" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="V3" s="70" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="W3" s="73" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="X3" s="79"/>
       <c r="Y3" s="82"/>
@@ -1777,10 +1798,10 @@
         <v>33</v>
       </c>
       <c r="H4" s="41" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I4" s="46" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J4" s="34" t="n">
         <v>37</v>
@@ -1808,23 +1829,23 @@
       </c>
       <c r="R4" s="57"/>
       <c r="S4" s="23" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="T4" s="62"/>
       <c r="U4" s="66" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="V4" s="66" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="W4" s="74" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="X4" s="74" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="Y4" s="83" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" s="88" customFormat="true">
@@ -1848,10 +1869,10 @@
         <v>34</v>
       </c>
       <c r="H5" s="42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I5" s="47" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="24"/>
@@ -1870,22 +1891,22 @@
         <v>42</v>
       </c>
       <c r="T5" s="23" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="U5" s="67" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="V5" s="67" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="W5" s="75" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="X5" s="75" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="Y5" s="84" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -1909,10 +1930,10 @@
         <v>35</v>
       </c>
       <c r="H6" s="24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I6" s="47" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J6" s="13"/>
       <c r="K6" s="24"/>
@@ -1931,22 +1952,22 @@
         <v>18</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="U6" s="67" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="V6" s="67" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="W6" s="75" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="X6" s="75" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="Y6" s="85" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -1969,10 +1990,10 @@
         <v>36</v>
       </c>
       <c r="H7" s="43" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I7" s="48" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J7" s="36"/>
       <c r="K7" s="25"/>
@@ -1991,22 +2012,22 @@
         <v>3</v>
       </c>
       <c r="T7" s="25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="U7" s="59" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="V7" s="59" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="W7" s="76" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="X7" s="76" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="Y7" s="86" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
@@ -2029,10 +2050,10 @@
         <v>37</v>
       </c>
       <c r="H8" s="43" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I8" s="48" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J8" s="36"/>
       <c r="K8" s="25"/>
@@ -2051,67 +2072,141 @@
         <v>1</v>
       </c>
       <c r="T8" s="25" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="U8" s="59" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="V8" s="59" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="W8" s="76" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="X8" s="76" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="Y8" s="86" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="18"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="19"/>
+      <c r="B9" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="24" t="n">
+        <v>20260514</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="48" t="s">
+        <v>51</v>
+      </c>
       <c r="J9" s="36"/>
       <c r="K9" s="25"/>
       <c r="L9" s="25"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
       <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
+      <c r="P9" s="25" t="n">
+        <v>36.763081</v>
+      </c>
+      <c r="Q9" s="25" t="n">
+        <v>127.090606</v>
+      </c>
       <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="25"/>
-      <c r="U9" s="59"/>
-      <c r="V9" s="59"/>
-      <c r="W9" s="76"/>
+      <c r="S9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="U9" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="V9" s="59" t="s">
+        <v>81</v>
+      </c>
+      <c r="W9" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="X9" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y9" s="86" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="18"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="19"/>
+      <c r="B10" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>20260514</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="48" t="s">
+        <v>51</v>
+      </c>
       <c r="J10" s="36"/>
       <c r="K10" s="25"/>
       <c r="L10" s="25"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
       <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="49"/>
+      <c r="P10" s="25" t="n">
+        <v>36.763081</v>
+      </c>
+      <c r="Q10" s="49" t="n">
+        <v>127.090606</v>
+      </c>
       <c r="R10" s="59"/>
       <c r="S10" s="25"/>
-      <c r="T10" s="25"/>
-      <c r="U10" s="59"/>
-      <c r="V10" s="59"/>
-      <c r="W10" s="76"/>
+      <c r="T10" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="U10" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="V10" s="59" t="s">
+        <v>82</v>
+      </c>
+      <c r="W10" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="X10" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y10" s="86" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="18"/>
@@ -7071,95 +7166,95 @@
   <sheetData>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="8" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="8" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="8" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="8" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="8" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="8" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18">
@@ -7167,13 +7262,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19">
@@ -7181,13 +7276,13 @@
         <v>2</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20">
@@ -7195,13 +7290,13 @@
         <v>3</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21">
@@ -7209,13 +7304,13 @@
         <v>4</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
@@ -7223,13 +7318,13 @@
         <v>5</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -7237,13 +7332,13 @@
         <v>6</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24">
@@ -7251,10 +7346,10 @@
         <v>7</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25">
@@ -7262,142 +7357,142 @@
         <v>8</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="8" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="8" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="8" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="8" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33">
       <c r="C33" s="8" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34">
       <c r="C34" s="8" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35">
       <c r="C35" s="8" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="8" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="8" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="8" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="8" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="8" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="8" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="8" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
